--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -1566,70 +1566,70 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46040.0)</f>
         <v>46040</v>
       </c>
-      <c r="B19" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),468.65)</f>
+        <v>468.65</v>
       </c>
       <c r="C19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="D19" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="E19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
+      </c>
+      <c r="F19" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="H19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="I19" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="J19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="K19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="L19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="O19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="P19" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),37.492)</f>
+        <v>37.492</v>
       </c>
       <c r="Q19" s="6"/>
       <c r="R19" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1653,9 +1653,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="F20" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="G20" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1699,8 +1699,8 @@
       </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="21">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -1637,65 +1637,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46041.0)</f>
         <v>46041</v>
       </c>
-      <c r="B20" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),490.25)</f>
+        <v>490.25</v>
       </c>
       <c r="C20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="D20" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="E20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="F20" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="G20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="H20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="I20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="J20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="K20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="L20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="M20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="N20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="O20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="P20" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.654545454545456)</f>
+        <v>35.65454545</v>
       </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -1708,65 +1708,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
         <v>46042</v>
       </c>
-      <c r="B21" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),479.6)</f>
+        <v>479.6</v>
       </c>
       <c r="C21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="D21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="E21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="F21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="H21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="I21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="J21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="L21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="O21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="P21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="Q21" s="6"/>
       <c r="R21" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -1708,65 +1708,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46042.0)</f>
         <v>46042</v>
       </c>
-      <c r="B21" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),479.6)</f>
+        <v>479.6</v>
       </c>
       <c r="C21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="D21" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="E21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="F21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="H21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="I21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="J21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="K21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="L21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="O21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="P21" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.973333333333336)</f>
+        <v>31.97333333</v>
       </c>
       <c r="Q21" s="6"/>
       <c r="R21" s="6">
@@ -1779,70 +1779,70 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
         <v>46043</v>
       </c>
-      <c r="B22" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),597.65)</f>
+        <v>597.65</v>
       </c>
       <c r="C22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="D22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="E22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="F22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="H22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="J22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
+      </c>
+      <c r="L22" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="O22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="P22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1890,9 +1890,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="L23" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="M23" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1912,8 +1912,8 @@
       </c>
       <c r="Q23" s="6"/>
       <c r="R23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="24">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -1779,70 +1779,70 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46043.0)</f>
         <v>46043</v>
       </c>
-      <c r="B22" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),597.65)</f>
+        <v>597.65</v>
       </c>
       <c r="C22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="D22" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="E22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="F22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="H22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="J22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="K22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
+      </c>
+      <c r="L22" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="O22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="P22" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.46545454545454)</f>
+        <v>43.46545455</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1850,70 +1850,70 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46044.0)</f>
         <v>46044</v>
       </c>
-      <c r="B23" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),476.2)</f>
+        <v>476.2</v>
       </c>
       <c r="C23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="D23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="E23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="F23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="G23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="H23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="I23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="J23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="K23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
+      </c>
+      <c r="L23" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="M23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="N23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="O23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="P23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.63272727272727)</f>
+        <v>34.63272727</v>
       </c>
       <c r="Q23" s="6"/>
       <c r="R23" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="24">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -1921,65 +1921,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46045.0)</f>
         <v>46045</v>
       </c>
-      <c r="B24" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),684.9)</f>
+        <v>684.9</v>
       </c>
       <c r="C24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="D24" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="E24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="F24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="G24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="H24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="I24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="J24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="K24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="L24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="M24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="N24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="O24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="P24" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.66)</f>
+        <v>45.66</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -1992,65 +1992,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46046.0)</f>
         <v>46046</v>
       </c>
-      <c r="B25" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),693.65)</f>
+        <v>693.65</v>
       </c>
       <c r="C25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="D25" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="E25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="F25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="G25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="H25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="I25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="J25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="K25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="L25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="M25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="N25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="O25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="P25" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.24333333333333)</f>
+        <v>46.24333333</v>
       </c>
       <c r="Q25" s="6"/>
       <c r="R25" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -2063,65 +2063,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
         <v>46047</v>
       </c>
-      <c r="B26" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.1)</f>
+        <v>470.1</v>
       </c>
       <c r="C26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="D26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="E26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="F26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="H26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="I26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="J26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="L26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="O26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="P26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -2063,65 +2063,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46047.0)</f>
         <v>46047</v>
       </c>
-      <c r="B26" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),470.1)</f>
+        <v>470.1</v>
       </c>
       <c r="C26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="D26" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="E26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="F26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="H26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="I26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="J26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="K26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="L26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="O26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="P26" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.340000000000003)</f>
+        <v>31.34</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6">
@@ -2134,65 +2134,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46048.0)</f>
         <v>46048</v>
       </c>
-      <c r="B27" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B27" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),484.95)</f>
+        <v>484.95</v>
       </c>
       <c r="C27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="D27" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="E27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="F27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="G27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="H27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="I27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="J27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="K27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="L27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="M27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="N27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="O27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="P27" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.33)</f>
+        <v>32.33</v>
       </c>
       <c r="Q27" s="6"/>
       <c r="R27" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -2205,65 +2205,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46049.0)</f>
         <v>46049</v>
       </c>
-      <c r="B28" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B28" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),530.4)</f>
+        <v>530.4</v>
       </c>
       <c r="C28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="D28" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="E28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="F28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="G28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="H28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="I28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="J28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="K28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="L28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="M28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="N28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="O28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="P28" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.36)</f>
+        <v>35.36</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -2276,65 +2276,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46050.0)</f>
         <v>46050</v>
       </c>
-      <c r="B29" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B29" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),500.95)</f>
+        <v>500.95</v>
       </c>
       <c r="C29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="D29" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="E29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="F29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="G29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="H29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="I29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="J29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="K29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="L29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="M29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="N29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="O29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="P29" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),33.39666666666666)</f>
+        <v>33.39666667</v>
       </c>
       <c r="Q29" s="6"/>
       <c r="R29" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -2347,65 +2347,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46051.0)</f>
         <v>46051</v>
       </c>
-      <c r="B30" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B30" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),534.55)</f>
+        <v>534.55</v>
       </c>
       <c r="C30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="D30" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="E30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="F30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="G30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="H30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="I30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="J30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="K30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="L30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="M30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="O30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="P30" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.63666666666666)</f>
+        <v>35.63666667</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6">

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -2418,70 +2418,70 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46052.0)</f>
         <v>46052</v>
       </c>
-      <c r="B31" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B31" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),507.8)</f>
+        <v>507.8</v>
       </c>
       <c r="C31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="D31" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="E31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="F31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
+      </c>
+      <c r="G31" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="H31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="I31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="J31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="K31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
+      </c>
+      <c r="L31" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="M31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="N31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="O31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="P31" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.624)</f>
+        <v>40.624</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -2509,9 +2509,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="G32" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="H32" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2529,9 +2529,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="L32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="L32" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
+        <v>x</v>
       </c>
       <c r="M32" s="5">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2551,8 +2551,8 @@
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/base_bps_comissao.xlsx
+++ b/base_bps_comissao.xlsx
@@ -2489,65 +2489,65 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46053.0)</f>
         <v>46053</v>
       </c>
-      <c r="B32" s="4" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="B32" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),617.2)</f>
+        <v>617.2</v>
       </c>
       <c r="C32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="D32" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="E32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="F32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="G32" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="H32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="I32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="J32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="K32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="L32" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"x")</f>
         <v>x</v>
       </c>
       <c r="M32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="N32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="O32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="P32" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.376000000000005)</f>
+        <v>49.376</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6">
